--- a/sakal/docs/Tenant/Shanju_COA_Import_Upload.xlsx
+++ b/sakal/docs/Tenant/Shanju_COA_Import_Upload.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="COA Import" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -50,7 +49,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -414,7 +413,23 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:P139"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <cols>
+    <col width="17.6328125" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="41.90625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="8.90625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="18.36328125" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="16.54296875" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="22.6328125" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="8.26953125" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="9.54296875" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="13.453125" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="6.08984375" bestFit="1" customWidth="1" min="10" max="10"/>
+    <col width="5.36328125" bestFit="1" customWidth="1" min="11" max="11"/>
+    <col width="12.90625" bestFit="1" customWidth="1" min="12" max="13"/>
+    <col width="6" bestFit="1" customWidth="1" min="14" max="14"/>
+    <col width="10.26953125" bestFit="1" customWidth="1" min="15" max="16"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -516,7 +531,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1200-001</t>
+          <t>1200296</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -548,7 +563,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1200-002</t>
+          <t>1200297</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -580,7 +595,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1200-003</t>
+          <t>1200298</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -612,7 +627,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1100-001</t>
+          <t>1100161</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -644,7 +659,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1100-002</t>
+          <t>1100162</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -676,7 +691,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>5200-001</t>
+          <t>5200261</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -708,7 +723,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1120-001</t>
+          <t>1120001</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -740,7 +755,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2110-001</t>
+          <t>2110001</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -772,7 +787,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1120-002</t>
+          <t>1120002</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -804,7 +819,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1120-003</t>
+          <t>1120003</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -836,7 +851,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1120-004</t>
+          <t>1120004</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -868,7 +883,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1120-005</t>
+          <t>1120005</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -900,7 +915,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1200-004</t>
+          <t>1200299</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -932,7 +947,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1200-005</t>
+          <t>1200300</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -964,7 +979,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1120-006</t>
+          <t>1120006</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -996,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2110-002</t>
+          <t>2110002</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1028,7 +1043,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1200-006</t>
+          <t>1200301</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1060,7 +1075,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2110-003</t>
+          <t>2110003</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1092,7 +1107,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1120-007</t>
+          <t>1120007</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1124,7 +1139,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1110-001</t>
+          <t>1110001</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1156,7 +1171,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1110-002</t>
+          <t>1110002</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1188,7 +1203,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2110-004</t>
+          <t>2110004</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1220,7 +1235,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1120-008</t>
+          <t>1120008</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1252,7 +1267,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1100-003</t>
+          <t>1100163</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1284,7 +1299,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1120-009</t>
+          <t>1120009</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1316,7 +1331,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>5200-002</t>
+          <t>5200262</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1348,7 +1363,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>4200-001</t>
+          <t>4200231</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1380,7 +1395,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>5200-003</t>
+          <t>5200263</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1412,7 +1427,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>5200-004</t>
+          <t>5200264</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1444,7 +1459,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>5200-005</t>
+          <t>5200265</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1476,7 +1491,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>5200-006</t>
+          <t>5200266</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1508,7 +1523,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>5200-007</t>
+          <t>5200267</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1540,7 +1555,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1120-010</t>
+          <t>1120010</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1572,7 +1587,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2110-005</t>
+          <t>2110005</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1604,7 +1619,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1120-011</t>
+          <t>1120011</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1636,7 +1651,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1120-012</t>
+          <t>1120012</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1668,7 +1683,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>5200-008</t>
+          <t>5200268</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1700,7 +1715,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2110-006</t>
+          <t>2110006</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1732,7 +1747,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1120-013</t>
+          <t>1120013</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1764,7 +1779,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1120-014</t>
+          <t>1120014</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1796,7 +1811,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1120-015</t>
+          <t>1120015</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1828,7 +1843,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1120-016</t>
+          <t>1120016</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1860,7 +1875,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1120-017</t>
+          <t>1120017</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1892,7 +1907,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>5200-009</t>
+          <t>5200269</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1924,7 +1939,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>5200-010</t>
+          <t>5200270</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1956,7 +1971,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>4200-002</t>
+          <t>4200232</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1988,7 +2003,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1110-003</t>
+          <t>1110003</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2020,7 +2035,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1110-004</t>
+          <t>1110004</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2052,7 +2067,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1120-018</t>
+          <t>1120018</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2084,7 +2099,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1120-019</t>
+          <t>1120019</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2116,7 +2131,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1120-020</t>
+          <t>1120020</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2148,7 +2163,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2110-007</t>
+          <t>2110007</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2180,7 +2195,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>5200-011</t>
+          <t>5200271</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2212,7 +2227,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2110-008</t>
+          <t>2110008</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2244,7 +2259,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1120-021</t>
+          <t>1120021</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2276,7 +2291,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>5200-012</t>
+          <t>5200272</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2308,7 +2323,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2110-009</t>
+          <t>2110009</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2340,7 +2355,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2110-010</t>
+          <t>2110010</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2372,7 +2387,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2110-011</t>
+          <t>2110011</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2404,7 +2419,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2110-012</t>
+          <t>2110012</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2436,7 +2451,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1120-022</t>
+          <t>1120022</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2468,7 +2483,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1120-023</t>
+          <t>1120023</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2500,7 +2515,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>5200-013</t>
+          <t>5200273</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2532,7 +2547,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2100-001</t>
+          <t>2100172</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2564,7 +2579,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>5200-014</t>
+          <t>5200274</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2596,7 +2611,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2100-002</t>
+          <t>2100173</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2628,7 +2643,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1120-024</t>
+          <t>1120024</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2660,7 +2675,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2100-003</t>
+          <t>2100174</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2692,7 +2707,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1120-025</t>
+          <t>1120025</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2724,7 +2739,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2110-013</t>
+          <t>2110013</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2756,7 +2771,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1120-026</t>
+          <t>1120026</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2788,7 +2803,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>5200-015</t>
+          <t>5200275</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2820,7 +2835,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2110-014</t>
+          <t>2110014</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -2852,7 +2867,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>5200-016</t>
+          <t>5200276</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -2884,7 +2899,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>5100-001</t>
+          <t>5100142</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -2916,7 +2931,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>5100-002</t>
+          <t>5100143</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -2948,7 +2963,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>5100-003</t>
+          <t>5100144</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -2980,7 +2995,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>5100-004</t>
+          <t>5100145</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3012,7 +3027,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>5100-005</t>
+          <t>5100146</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3044,7 +3059,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>5100-006</t>
+          <t>5100147</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3076,7 +3091,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>5100-007</t>
+          <t>5100148</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3108,7 +3123,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>5100-008</t>
+          <t>5100149</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3140,7 +3155,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>5100-009</t>
+          <t>5100150</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3172,7 +3187,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>5100-010</t>
+          <t>5100151</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3204,7 +3219,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>5100-011</t>
+          <t>5100152</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3236,7 +3251,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>5100-012</t>
+          <t>5100153</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3268,7 +3283,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>5100-013</t>
+          <t>5100154</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3300,7 +3315,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>5100-014</t>
+          <t>5100155</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3332,7 +3347,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1200-007</t>
+          <t>1200302</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3364,7 +3379,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>5300-001</t>
+          <t>5300331</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3396,7 +3411,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>5200-017</t>
+          <t>5200277</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3428,7 +3443,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>5200-018</t>
+          <t>5200278</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3460,7 +3475,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1120-027</t>
+          <t>1120027</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3492,7 +3507,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>5200-019</t>
+          <t>5200279</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3524,7 +3539,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1120-028</t>
+          <t>1120028</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3556,7 +3571,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2110-015</t>
+          <t>2110015</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3588,7 +3603,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>5200-020</t>
+          <t>5200280</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3620,7 +3635,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>4100-001</t>
+          <t>4100141</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3652,7 +3667,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>4100-002</t>
+          <t>4100142</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3684,7 +3699,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>4100-003</t>
+          <t>4100143</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3716,7 +3731,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>4100-004</t>
+          <t>4100144</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3748,7 +3763,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>4100-005</t>
+          <t>4100145</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -3780,7 +3795,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>4100-006</t>
+          <t>4100146</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -3812,7 +3827,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>4100-007</t>
+          <t>4100147</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -3844,7 +3859,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>4100-008</t>
+          <t>4100148</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -3876,7 +3891,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>4100-009</t>
+          <t>4100149</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -3908,7 +3923,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>4100-010</t>
+          <t>4100150</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -3940,7 +3955,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>4100-011</t>
+          <t>4100151</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -3972,7 +3987,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2110-016</t>
+          <t>2110016</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4004,7 +4019,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>1120-029</t>
+          <t>1120029</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4036,7 +4051,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>1120-030</t>
+          <t>1120030</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4068,7 +4083,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>1120-031</t>
+          <t>1120031</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4100,7 +4115,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>1100-004</t>
+          <t>1100164</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4132,7 +4147,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2110-017</t>
+          <t>2110017</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4164,7 +4179,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2110-018</t>
+          <t>2110018</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4196,7 +4211,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>1120-032</t>
+          <t>1120032</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4228,7 +4243,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2110-019</t>
+          <t>2110019</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4260,7 +4275,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>1120-033</t>
+          <t>1120033</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4292,7 +4307,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2110-020</t>
+          <t>2110020</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4324,7 +4339,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2110-021</t>
+          <t>2110021</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4356,7 +4371,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2110-022</t>
+          <t>2110022</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4388,7 +4403,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>5200-021</t>
+          <t>5200281</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4420,7 +4435,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2110-023</t>
+          <t>2110023</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4452,7 +4467,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>1120-034</t>
+          <t>1120034</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4484,7 +4499,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>5200-022</t>
+          <t>5200282</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4516,7 +4531,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>5200-023</t>
+          <t>5200283</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4548,7 +4563,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>1120-035</t>
+          <t>1120035</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4580,7 +4595,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2110-024</t>
+          <t>2110024</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4612,7 +4627,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>5300-002</t>
+          <t>5300332</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4644,7 +4659,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>1120-036</t>
+          <t>1120036</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -4676,7 +4691,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2110-025</t>
+          <t>2110025</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -4708,7 +4723,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>1120-037</t>
+          <t>1120037</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -4740,7 +4755,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>1120-038</t>
+          <t>1120038</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -4772,7 +4787,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2110-026</t>
+          <t>2110026</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -4804,7 +4819,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>1100-005</t>
+          <t>1100165</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -4836,7 +4851,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>1120-039</t>
+          <t>1120039</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -4868,7 +4883,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>1120-040</t>
+          <t>1120040</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -4900,7 +4915,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>1120-041</t>
+          <t>1120041</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
